--- a/data/Bundesliga.xlsx
+++ b/data/Bundesliga.xlsx
@@ -23,13 +23,27 @@
     <sheet sheetId="12" name="Jornada 32" state="visible" r:id="rId17"/>
     <sheet sheetId="13" name="Jornada 33" state="visible" r:id="rId18"/>
     <sheet sheetId="14" name="Jornada 34" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="Jornada 1" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="Jornada 2" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="Jornada 3" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="Jornada 4" state="visible" r:id="rId23"/>
+    <sheet sheetId="21" name="Jornada 5" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Jornada 6" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Jornada 7" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Jornada 8" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Jornada 9" state="visible" r:id="rId28"/>
+    <sheet sheetId="26" name="Jornada 10" state="visible" r:id="rId29"/>
+    <sheet sheetId="27" name="Jornada 11" state="visible" r:id="rId30"/>
+    <sheet sheetId="28" name="Jornada 12" state="visible" r:id="rId31"/>
+    <sheet sheetId="29" name="Jornada 13" state="visible" r:id="rId32"/>
+    <sheet sheetId="30" name="Jornada 14" state="visible" r:id="rId33"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="133">
   <si>
     <t>Matchday</t>
   </si>
@@ -311,6 +325,123 @@
   </si>
   <si>
     <t>16/05/2026</t>
+  </si>
+  <si>
+    <t>Jornada 1</t>
+  </si>
+  <si>
+    <t>28/08/2026</t>
+  </si>
+  <si>
+    <t>29/08/2026</t>
+  </si>
+  <si>
+    <t>SC Paderborn</t>
+  </si>
+  <si>
+    <t>SV Elversberg</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>FC Schalke 04</t>
+  </si>
+  <si>
+    <t>Jornada 2</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>05/09/2026</t>
+  </si>
+  <si>
+    <t>06/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 3</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>12/09/2026</t>
+  </si>
+  <si>
+    <t>13/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 4</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>20/09/2026</t>
+  </si>
+  <si>
+    <t>Jornada 5</t>
+  </si>
+  <si>
+    <t>10/10/2026</t>
+  </si>
+  <si>
+    <t>Jornada 6</t>
+  </si>
+  <si>
+    <t>17/10/2026</t>
+  </si>
+  <si>
+    <t>Jornada 7</t>
+  </si>
+  <si>
+    <t>24/10/2026</t>
+  </si>
+  <si>
+    <t>Jornada 8</t>
+  </si>
+  <si>
+    <t>31/10/2026</t>
+  </si>
+  <si>
+    <t>Jornada 9</t>
+  </si>
+  <si>
+    <t>07/11/2026</t>
+  </si>
+  <si>
+    <t>Jornada 10</t>
+  </si>
+  <si>
+    <t>21/11/2026</t>
+  </si>
+  <si>
+    <t>Jornada 11</t>
+  </si>
+  <si>
+    <t>28/11/2026</t>
+  </si>
+  <si>
+    <t>Jornada 12</t>
+  </si>
+  <si>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>Jornada 13</t>
+  </si>
+  <si>
+    <t>12/12/2026</t>
+  </si>
+  <si>
+    <t>Jornada 14</t>
+  </si>
+  <si>
+    <t>19/12/2026</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2321,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2692,6 +2823,753 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G10"/>
@@ -2930,6 +3808,2496 @@
       </c>
       <c r="F10" t="s">
         <v>24</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>116</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>121</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>126</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>128</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F10" t="s">
+        <v>98</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -3187,6 +6555,255 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>97</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 

--- a/data/Bundesliga.xlsx
+++ b/data/Bundesliga.xlsx
@@ -7,43 +7,43 @@
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="12"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="6" name="Jornada 26" state="visible" r:id="rId4"/>
-    <sheet sheetId="15" name="Jornada 19" state="visible" r:id="rId5"/>
-    <sheet sheetId="16" name="Jornada 20" state="visible" r:id="rId6"/>
-    <sheet sheetId="1" name="Jornada 21" state="visible" r:id="rId7"/>
-    <sheet sheetId="2" name="Jornada 22" state="visible" r:id="rId8"/>
-    <sheet sheetId="3" name="Jornada 23" state="visible" r:id="rId9"/>
-    <sheet sheetId="4" name="Jornada 24" state="visible" r:id="rId10"/>
-    <sheet sheetId="5" name="Jornada 25" state="visible" r:id="rId11"/>
-    <sheet sheetId="7" name="Jornada 27" state="visible" r:id="rId12"/>
-    <sheet sheetId="8" name="Jornada 28" state="visible" r:id="rId13"/>
-    <sheet sheetId="9" name="Jornada 29" state="visible" r:id="rId14"/>
-    <sheet sheetId="10" name="Jornada 30" state="visible" r:id="rId15"/>
-    <sheet sheetId="11" name="Jornada 31" state="visible" r:id="rId16"/>
-    <sheet sheetId="12" name="Jornada 32" state="visible" r:id="rId17"/>
-    <sheet sheetId="13" name="Jornada 33" state="visible" r:id="rId18"/>
-    <sheet sheetId="14" name="Jornada 34" state="visible" r:id="rId19"/>
-    <sheet sheetId="17" name="Jornada 1" state="visible" r:id="rId20"/>
-    <sheet sheetId="18" name="Jornada 2" state="visible" r:id="rId21"/>
-    <sheet sheetId="19" name="Jornada 3" state="visible" r:id="rId22"/>
-    <sheet sheetId="20" name="Jornada 4" state="visible" r:id="rId23"/>
-    <sheet sheetId="21" name="Jornada 5" state="visible" r:id="rId24"/>
-    <sheet sheetId="22" name="Jornada 6" state="visible" r:id="rId25"/>
-    <sheet sheetId="23" name="Jornada 7" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Jornada 8" state="visible" r:id="rId27"/>
-    <sheet sheetId="25" name="Jornada 9" state="visible" r:id="rId28"/>
-    <sheet sheetId="26" name="Jornada 10" state="visible" r:id="rId29"/>
-    <sheet sheetId="27" name="Jornada 11" state="visible" r:id="rId30"/>
-    <sheet sheetId="28" name="Jornada 12" state="visible" r:id="rId31"/>
-    <sheet sheetId="29" name="Jornada 13" state="visible" r:id="rId32"/>
-    <sheet sheetId="30" name="Jornada 14" state="visible" r:id="rId33"/>
+    <sheet sheetId="17" name="Jornada 1" state="visible" r:id="rId4"/>
+    <sheet sheetId="18" name="Jornada 2" state="visible" r:id="rId5"/>
+    <sheet sheetId="19" name="Jornada 3" state="visible" r:id="rId6"/>
+    <sheet sheetId="20" name="Jornada 4" state="visible" r:id="rId7"/>
+    <sheet sheetId="21" name="Jornada 5" state="visible" r:id="rId8"/>
+    <sheet sheetId="22" name="Jornada 6" state="visible" r:id="rId9"/>
+    <sheet sheetId="23" name="Jornada 7" state="visible" r:id="rId10"/>
+    <sheet sheetId="24" name="Jornada 8" state="visible" r:id="rId11"/>
+    <sheet sheetId="25" name="Jornada 9" state="visible" r:id="rId12"/>
+    <sheet sheetId="26" name="Jornada 10" state="visible" r:id="rId13"/>
+    <sheet sheetId="27" name="Jornada 11" state="visible" r:id="rId14"/>
+    <sheet sheetId="28" name="Jornada 12" state="visible" r:id="rId15"/>
+    <sheet sheetId="29" name="Jornada 13" state="visible" r:id="rId16"/>
+    <sheet sheetId="30" name="Jornada 14" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="Jornada 19" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="Jornada 20" state="visible" r:id="rId19"/>
+    <sheet sheetId="1" name="Jornada 21" state="visible" r:id="rId20"/>
+    <sheet sheetId="2" name="Jornada 22" state="visible" r:id="rId21"/>
+    <sheet sheetId="3" name="Jornada 23" state="visible" r:id="rId22"/>
+    <sheet sheetId="4" name="Jornada 24" state="visible" r:id="rId23"/>
+    <sheet sheetId="5" name="Jornada 25" state="visible" r:id="rId24"/>
+    <sheet sheetId="6" name="Jornada 26" state="visible" r:id="rId25"/>
+    <sheet sheetId="7" name="Jornada 27" state="visible" r:id="rId26"/>
+    <sheet sheetId="8" name="Jornada 28" state="visible" r:id="rId27"/>
+    <sheet sheetId="9" name="Jornada 29" state="visible" r:id="rId28"/>
+    <sheet sheetId="10" name="Jornada 30" state="visible" r:id="rId29"/>
+    <sheet sheetId="11" name="Jornada 31" state="visible" r:id="rId30"/>
+    <sheet sheetId="12" name="Jornada 32" state="visible" r:id="rId31"/>
+    <sheet sheetId="13" name="Jornada 33" state="visible" r:id="rId32"/>
+    <sheet sheetId="14" name="Jornada 34" state="visible" r:id="rId33"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="189">
   <si>
     <t>Matchday</t>
   </si>
@@ -66,398 +66,561 @@
     <t>Score</t>
   </si>
   <si>
+    <t>Jornada 1</t>
+  </si>
+  <si>
+    <t>Friday</t>
+  </si>
+  <si>
+    <t>10/01/2025</t>
+  </si>
+  <si>
+    <t>3:45 PM</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Bayer Leverkusen</t>
+  </si>
+  <si>
+    <t>2:3</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>11/01/2025</t>
+  </si>
+  <si>
+    <t>10:30 AM</t>
+  </si>
+  <si>
+    <t>1. FC Heidenheim 1846</t>
+  </si>
+  <si>
+    <t>1. FC Union Berlin</t>
+  </si>
+  <si>
+    <t>2:0</t>
+  </si>
+  <si>
+    <t>Mainz</t>
+  </si>
+  <si>
+    <t>VfL Bochum</t>
+  </si>
+  <si>
+    <t>SC Freiburg</t>
+  </si>
+  <si>
+    <t>Holstein Kiel</t>
+  </si>
+  <si>
+    <t>3:2</t>
+  </si>
+  <si>
+    <t>St. Pauli</t>
+  </si>
+  <si>
+    <t>Eintracht Frankfurt</t>
+  </si>
+  <si>
+    <t>0:1</t>
+  </si>
+  <si>
+    <t>TSG Hoffenheim</t>
+  </si>
+  <si>
+    <t>VfL Wolfsburg</t>
+  </si>
+  <si>
+    <t>1:30 PM</t>
+  </si>
+  <si>
+    <t>Borussia Mönchengladbach</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>12/01/2025</t>
+  </si>
+  <si>
+    <t>RB Leipzig</t>
+  </si>
+  <si>
+    <t>Werder Bremen</t>
+  </si>
+  <si>
+    <t>4:2</t>
+  </si>
+  <si>
+    <t>12:30 PM</t>
+  </si>
+  <si>
+    <t>FC Augsburg</t>
+  </si>
+  <si>
+    <t>VfB Stuttgart</t>
+  </si>
+  <si>
+    <t>Jornada 2</t>
+  </si>
+  <si>
+    <t>Tuesday</t>
+  </si>
+  <si>
+    <t>14/01/2025</t>
+  </si>
+  <si>
+    <t>3:30 PM</t>
+  </si>
+  <si>
+    <t>1:0</t>
+  </si>
+  <si>
+    <t>4:1</t>
+  </si>
+  <si>
+    <t>5:1</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
+  </si>
+  <si>
+    <t>15/01/2025</t>
+  </si>
+  <si>
+    <t>0:2</t>
+  </si>
+  <si>
+    <t>5:0</t>
+  </si>
+  <si>
+    <t>2:1</t>
+  </si>
+  <si>
+    <t>3:3</t>
+  </si>
+  <si>
+    <t>Jornada 3</t>
+  </si>
+  <si>
+    <t>17/01/2025</t>
+  </si>
+  <si>
+    <t>18/01/2025</t>
+  </si>
+  <si>
+    <t>1:3</t>
+  </si>
+  <si>
+    <t>4:0</t>
+  </si>
+  <si>
+    <t>3:1</t>
+  </si>
+  <si>
+    <t>19/01/2025</t>
+  </si>
+  <si>
+    <t>Jornada 4</t>
+  </si>
+  <si>
+    <t>24/01/2025</t>
+  </si>
+  <si>
+    <t>2:2</t>
+  </si>
+  <si>
+    <t>25/01/2025</t>
+  </si>
+  <si>
+    <t>1:2</t>
+  </si>
+  <si>
+    <t>3:0</t>
+  </si>
+  <si>
+    <t>26/01/2025</t>
+  </si>
+  <si>
+    <t>Jornada 5</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>01/02/2025</t>
+  </si>
+  <si>
+    <t>4:3</t>
+  </si>
+  <si>
+    <t>1:1</t>
+  </si>
+  <si>
+    <t>0:0</t>
+  </si>
+  <si>
+    <t>02/02/2025</t>
+  </si>
+  <si>
+    <t>Jornada 6</t>
+  </si>
+  <si>
+    <t>07/02/2025</t>
+  </si>
+  <si>
+    <t>08/02/2025</t>
+  </si>
+  <si>
+    <t>0:4</t>
+  </si>
+  <si>
+    <t>09/02/2025</t>
+  </si>
+  <si>
+    <t>Jornada 7</t>
+  </si>
+  <si>
+    <t>14/02/2025</t>
+  </si>
+  <si>
+    <t>15/02/2025</t>
+  </si>
+  <si>
+    <t>16/02/2025</t>
+  </si>
+  <si>
+    <t>2:30 PM</t>
+  </si>
+  <si>
+    <t>Jornada 8</t>
+  </si>
+  <si>
+    <t>21/02/2025</t>
+  </si>
+  <si>
+    <t>22/02/2025</t>
+  </si>
+  <si>
+    <t>0:3</t>
+  </si>
+  <si>
+    <t>6:0</t>
+  </si>
+  <si>
+    <t>23/02/2025</t>
+  </si>
+  <si>
+    <t>Jornada 9</t>
+  </si>
+  <si>
+    <t>28/02/2025</t>
+  </si>
+  <si>
+    <t>01/03/2025</t>
+  </si>
+  <si>
+    <t>1:4</t>
+  </si>
+  <si>
+    <t>02/03/2025</t>
+  </si>
+  <si>
+    <t>Jornada 10</t>
+  </si>
+  <si>
+    <t>07/03/2025</t>
+  </si>
+  <si>
+    <t>08/03/2025</t>
+  </si>
+  <si>
+    <t>09/03/2025</t>
+  </si>
+  <si>
+    <t>Jornada 11</t>
+  </si>
+  <si>
+    <t>14/03/2025</t>
+  </si>
+  <si>
+    <t>15/03/2025</t>
+  </si>
+  <si>
+    <t>2:4</t>
+  </si>
+  <si>
+    <t>16/03/2025</t>
+  </si>
+  <si>
+    <t>3:4</t>
+  </si>
+  <si>
+    <t>Jornada 12</t>
+  </si>
+  <si>
+    <t>28/03/2025</t>
+  </si>
+  <si>
+    <t>29/03/2025</t>
+  </si>
+  <si>
+    <t>30/03/2025</t>
+  </si>
+  <si>
+    <t>9:30 AM</t>
+  </si>
+  <si>
+    <t>11:30 AM</t>
+  </si>
+  <si>
+    <t>Jornada 13</t>
+  </si>
+  <si>
+    <t>04/04/2025</t>
+  </si>
+  <si>
+    <t>05/04/2025</t>
+  </si>
+  <si>
+    <t>06/04/2025</t>
+  </si>
+  <si>
+    <t>Jornada 14</t>
+  </si>
+  <si>
+    <t>11/04/2025</t>
+  </si>
+  <si>
+    <t>12/04/2025</t>
+  </si>
+  <si>
+    <t>13/04/2025</t>
+  </si>
+  <si>
+    <t>Jornada 19</t>
+  </si>
+  <si>
+    <t>17/05/2025</t>
+  </si>
+  <si>
+    <t>Jornada 20</t>
+  </si>
+  <si>
+    <t>22/08/2025</t>
+  </si>
+  <si>
+    <t>23/08/2025</t>
+  </si>
+  <si>
+    <t>24/08/2025</t>
+  </si>
+  <si>
+    <t>FC Cologne</t>
+  </si>
+  <si>
+    <t>Hamburg SV</t>
+  </si>
+  <si>
+    <t>Jornada 21</t>
+  </si>
+  <si>
+    <t>29/08/2025</t>
+  </si>
+  <si>
+    <t>30/08/2025</t>
+  </si>
+  <si>
+    <t>31/08/2025</t>
+  </si>
+  <si>
+    <t>Jornada 22</t>
+  </si>
+  <si>
+    <t>12/09/2025</t>
+  </si>
+  <si>
+    <t>13/09/2025</t>
+  </si>
+  <si>
+    <t>14/09/2025</t>
+  </si>
+  <si>
+    <t>Jornada 23</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>20/09/2025</t>
+  </si>
+  <si>
+    <t>21/09/2025</t>
+  </si>
+  <si>
+    <t>Jornada 24</t>
+  </si>
+  <si>
+    <t>26/09/2025</t>
+  </si>
+  <si>
+    <t>27/09/2025</t>
+  </si>
+  <si>
+    <t>4:6</t>
+  </si>
+  <si>
+    <t>28/09/2025</t>
+  </si>
+  <si>
+    <t>Jornada 25</t>
+  </si>
+  <si>
+    <t>03/10/2025</t>
+  </si>
+  <si>
+    <t>04/10/2025</t>
+  </si>
+  <si>
+    <t>05/10/2025</t>
+  </si>
+  <si>
     <t>Jornada 26</t>
   </si>
   <si>
-    <t>Friday</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>3:30 PM</t>
-  </si>
-  <si>
-    <t>Mönchengladbach</t>
-  </si>
-  <si>
-    <t>St. Pauli</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Saturday</t>
-  </si>
-  <si>
-    <t>14/03/2026</t>
-  </si>
-  <si>
-    <t>10:30 AM</t>
-  </si>
-  <si>
-    <t>Leverkusen</t>
-  </si>
-  <si>
-    <t>Bayern Munich</t>
-  </si>
-  <si>
-    <t>Frankfurt</t>
-  </si>
-  <si>
-    <t>Heidenheim</t>
-  </si>
-  <si>
-    <t>Dortmund</t>
-  </si>
-  <si>
-    <t>Augsburg</t>
-  </si>
-  <si>
-    <t>Hoffenheim</t>
-  </si>
-  <si>
-    <t>Wolfsburg</t>
-  </si>
-  <si>
-    <t>1:30 PM</t>
-  </si>
-  <si>
-    <t>Hamburg</t>
-  </si>
-  <si>
-    <t>1.FC Köln</t>
-  </si>
-  <si>
-    <t>Sunday</t>
-  </si>
-  <si>
-    <t>15/03/2026</t>
-  </si>
-  <si>
-    <t>Werder Bremen</t>
-  </si>
-  <si>
-    <t>Mainz</t>
-  </si>
-  <si>
-    <t>12:30 PM</t>
-  </si>
-  <si>
-    <t>Freiburg</t>
-  </si>
-  <si>
-    <t>Union Berlin</t>
-  </si>
-  <si>
-    <t>2:30 PM</t>
-  </si>
-  <si>
-    <t>Stuttgart</t>
-  </si>
-  <si>
-    <t>Leipzig</t>
-  </si>
-  <si>
-    <t>Jornada 19</t>
-  </si>
-  <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>24/01/2026</t>
-  </si>
-  <si>
-    <t>25/01/2026</t>
-  </si>
-  <si>
-    <t>Jornada 20</t>
-  </si>
-  <si>
-    <t>30/01/2026</t>
-  </si>
-  <si>
-    <t>31/01/2026</t>
-  </si>
-  <si>
-    <t>01/02/2026</t>
-  </si>
-  <si>
-    <t>Jornada 21</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>07/02/2026</t>
-  </si>
-  <si>
-    <t>08/02/2026</t>
-  </si>
-  <si>
-    <t>Jornada 22</t>
-  </si>
-  <si>
-    <t>13/02/2026</t>
-  </si>
-  <si>
-    <t>14/02/2026</t>
-  </si>
-  <si>
-    <t>15/02/2026</t>
-  </si>
-  <si>
-    <t>Jornada 23</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>21/02/2026</t>
-  </si>
-  <si>
-    <t>22/02/2026</t>
-  </si>
-  <si>
-    <t>Jornada 24</t>
-  </si>
-  <si>
-    <t>27/02/2026</t>
-  </si>
-  <si>
-    <t>28/02/2026</t>
-  </si>
-  <si>
-    <t>01/03/2026</t>
-  </si>
-  <si>
-    <t>Jornada 25</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>07/03/2026</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
+    <t>17/10/2025</t>
+  </si>
+  <si>
+    <t>18/10/2025</t>
+  </si>
+  <si>
+    <t>19/10/2025</t>
   </si>
   <si>
     <t>Jornada 27</t>
   </si>
   <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>21/03/2026</t>
-  </si>
-  <si>
-    <t>22/03/2026</t>
+    <t>24/10/2025</t>
+  </si>
+  <si>
+    <t>25/10/2025</t>
+  </si>
+  <si>
+    <t>0:6</t>
+  </si>
+  <si>
+    <t>9:45 AM</t>
+  </si>
+  <si>
+    <t>26/10/2025</t>
   </si>
   <si>
     <t>Jornada 28</t>
   </si>
   <si>
-    <t>04/04/2026</t>
-  </si>
-  <si>
-    <t>05/04/2026</t>
+    <t>31/10/2025</t>
+  </si>
+  <si>
+    <t>01/11/2025</t>
+  </si>
+  <si>
+    <t>02/11/2025</t>
   </si>
   <si>
     <t>Jornada 29</t>
   </si>
   <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>11/04/2026</t>
-  </si>
-  <si>
-    <t>12/04/2026</t>
+    <t>07/11/2025</t>
+  </si>
+  <si>
+    <t>08/11/2025</t>
+  </si>
+  <si>
+    <t>09/11/2025</t>
   </si>
   <si>
     <t>Jornada 30</t>
   </si>
   <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>18/04/2026</t>
-  </si>
-  <si>
-    <t>19/04/2026</t>
+    <t>21/11/2025</t>
+  </si>
+  <si>
+    <t>22/11/2025</t>
+  </si>
+  <si>
+    <t>6:2</t>
+  </si>
+  <si>
+    <t>23/11/2025</t>
   </si>
   <si>
     <t>Jornada 31</t>
   </si>
   <si>
-    <t>24/04/2026</t>
-  </si>
-  <si>
-    <t>25/04/2026</t>
-  </si>
-  <si>
-    <t>26/04/2026</t>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>29/11/2025</t>
+  </si>
+  <si>
+    <t>30/11/2025</t>
   </si>
   <si>
     <t>Jornada 32</t>
   </si>
   <si>
-    <t>02/05/2026</t>
-  </si>
-  <si>
-    <t>03/05/2026</t>
+    <t>05/12/2025</t>
+  </si>
+  <si>
+    <t>06/12/2025</t>
+  </si>
+  <si>
+    <t>0:5</t>
+  </si>
+  <si>
+    <t>07/12/2025</t>
   </si>
   <si>
     <t>Jornada 33</t>
   </si>
   <si>
-    <t>08/05/2026</t>
-  </si>
-  <si>
-    <t>09/05/2026</t>
-  </si>
-  <si>
-    <t>10/05/2026</t>
+    <t>12/12/2025</t>
+  </si>
+  <si>
+    <t>13/12/2025</t>
+  </si>
+  <si>
+    <t>14/12/2025</t>
   </si>
   <si>
     <t>Jornada 34</t>
   </si>
   <si>
-    <t>16/05/2026</t>
-  </si>
-  <si>
-    <t>Jornada 1</t>
-  </si>
-  <si>
-    <t>28/08/2026</t>
-  </si>
-  <si>
-    <t>29/08/2026</t>
-  </si>
-  <si>
-    <t>SC Paderborn</t>
-  </si>
-  <si>
-    <t>SV Elversberg</t>
-  </si>
-  <si>
-    <t>30/08/2026</t>
-  </si>
-  <si>
-    <t>FC Schalke 04</t>
-  </si>
-  <si>
-    <t>Jornada 2</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>05/09/2026</t>
-  </si>
-  <si>
-    <t>06/09/2026</t>
-  </si>
-  <si>
-    <t>Jornada 3</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>12/09/2026</t>
-  </si>
-  <si>
-    <t>13/09/2026</t>
-  </si>
-  <si>
-    <t>Jornada 4</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>19/09/2026</t>
-  </si>
-  <si>
-    <t>20/09/2026</t>
-  </si>
-  <si>
-    <t>Jornada 5</t>
-  </si>
-  <si>
-    <t>10/10/2026</t>
-  </si>
-  <si>
-    <t>Jornada 6</t>
-  </si>
-  <si>
-    <t>17/10/2026</t>
-  </si>
-  <si>
-    <t>Jornada 7</t>
-  </si>
-  <si>
-    <t>24/10/2026</t>
-  </si>
-  <si>
-    <t>Jornada 8</t>
-  </si>
-  <si>
-    <t>31/10/2026</t>
-  </si>
-  <si>
-    <t>Jornada 9</t>
-  </si>
-  <si>
-    <t>07/11/2026</t>
-  </si>
-  <si>
-    <t>Jornada 10</t>
-  </si>
-  <si>
-    <t>21/11/2026</t>
-  </si>
-  <si>
-    <t>Jornada 11</t>
-  </si>
-  <si>
-    <t>28/11/2026</t>
-  </si>
-  <si>
-    <t>Jornada 12</t>
-  </si>
-  <si>
-    <t>05/12/2026</t>
-  </si>
-  <si>
-    <t>Jornada 13</t>
-  </si>
-  <si>
-    <t>12/12/2026</t>
-  </si>
-  <si>
-    <t>Jornada 14</t>
-  </si>
-  <si>
-    <t>19/12/2026</t>
+    <t>19/12/2025</t>
+  </si>
+  <si>
+    <t>20/12/2025</t>
+  </si>
+  <si>
+    <t>21/12/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -490,10 +653,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -844,162 +1006,162 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>127</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -1007,71 +1169,71 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
         <v>46</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1093,61 +1255,61 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>168</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
@@ -1156,171 +1318,171 @@
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>169</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1342,234 +1504,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>175</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1591,234 +1753,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>177</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1840,234 +2002,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>127</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2089,239 +2251,239 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>188</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
@@ -2338,162 +2500,162 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" t="s">
-        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -2501,71 +2663,71 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D10" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>32</v>
       </c>
-      <c r="E10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
-      </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2587,234 +2749,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" t="s">
-        <v>26</v>
-      </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2836,47 +2998,47 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -2884,186 +3046,186 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
         <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3085,234 +3247,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -3334,234 +3496,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3583,234 +3745,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3832,234 +3994,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>100</v>
-      </c>
       <c r="F9" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -4081,234 +4243,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
-        <v>26</v>
-      </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4330,234 +4492,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4579,234 +4741,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4828,234 +4990,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -5077,234 +5239,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
         <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -5326,93 +5488,93 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
@@ -5420,140 +5582,140 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -5575,234 +5737,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -5824,234 +5986,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s">
         <v>27</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6073,234 +6235,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
-        <v>18</v>
-      </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>97</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -6322,234 +6484,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -6571,47 +6733,47 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
@@ -6619,191 +6781,191 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -6820,234 +6982,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>37</v>
+        <v>127</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -7069,234 +7231,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="F9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -7308,15 +7470,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="6" width="25" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -7344,209 +7505,209 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="C10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -7568,234 +7729,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>19</v>
+        <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7817,231 +7978,231 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D7" t="s">
         <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
       <c r="D9" t="s">
         <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>126</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>159</v>
       </c>
       <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
         <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
-        <v>27</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -8066,234 +8227,234 @@
     <col min="7" max="7" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D6" t="s">
         <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="D8" t="s">
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
